--- a/tests/batchtest.xlsx
+++ b/tests/batchtest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/jlagreca_student_unimelb_edu_au/Documents/PhD/Github/EQ-Scalculator/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CFFB8C1-876B-44C9-9DE0-1B0F1F547147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{3CFFB8C1-876B-44C9-9DE0-1B0F1F547147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8E269B4-FF8D-46E8-B7CE-86DD9402041B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E0B50120-770A-45C7-A2CA-B7E3647BD88F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E0B50120-770A-45C7-A2CA-B7E3647BD88F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Fault Name</t>
   </si>
@@ -63,6 +63,15 @@
   </si>
   <si>
     <t>Length</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Slip Rate</t>
+  </si>
+  <si>
+    <t>slip rate error</t>
   </si>
 </sst>
 </file>
@@ -115,6 +124,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,74 +447,153 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E74465-E6D1-4B62-98E7-2ACFC007DC7A}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2">
+        <f>B2*0.05</f>
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <f t="shared" ref="C3:C8" si="0">B3*0.05</f>
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>2.75</v>
+      </c>
+      <c r="D4">
+        <v>49</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <v>63.7</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>3.1850000000000005</v>
+      </c>
+      <c r="D5">
+        <v>52.08</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
         <v>44.32</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>2.2160000000000002</v>
+      </c>
+      <c r="D6">
+        <v>23.77</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
         <v>122</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>6.1000000000000005</v>
+      </c>
+      <c r="D7">
+        <v>45</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8">
         <v>346.58319999999998</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>17.329159999999998</v>
+      </c>
+      <c r="D8">
+        <v>101</v>
+      </c>
+      <c r="E8">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
